--- a/evaluations/classification/classification_results_grid_search_final.xlsx
+++ b/evaluations/classification/classification_results_grid_search_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y76"/>
+  <dimension ref="A1:Y88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,16 +690,16 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>6.75</v>
+        <v>6.73</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.7881</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7793</v>
+        <v>0.8462</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6855</v>
+        <v>0.7808</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -737,9 +737,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>256</v>
       </c>
@@ -769,24 +773,28 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.7289</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9382</v>
+        <v>0.8714</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8806</v>
+        <v>0.7083</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -800,16 +808,12 @@
       <c r="C5" t="n">
         <v>174</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -848,28 +852,24 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>6.76</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0.546</v>
+        <v>0.6936</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6936</v>
+        <v>0.8386</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5255</v>
+        <v>0.6715</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -885,14 +885,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -931,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>6.73</v>
+        <v>5.11</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7881</v>
+        <v>0.8815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8462</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7808</v>
+        <v>0.8749</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -975,14 +975,14 @@
         <v>1</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1014,16 +1014,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>8.85</v>
+        <v>6.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9899</v>
+        <v>0.5712</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9912</v>
+        <v>0.715</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.5518</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -1097,16 +1097,16 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>8.85</v>
+        <v>5.12</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8789</v>
+        <v>0.8058</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9332</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8692</v>
+        <v>0.7927</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5712</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.715</v>
+        <v>0.7793</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5518</v>
+        <v>0.6855</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1227,13 +1227,9 @@
         <v>0</v>
       </c>
       <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>resnet50</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>256</v>
       </c>
@@ -1263,28 +1259,24 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>8.83</v>
+        <v>5.06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.884</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9319</v>
+        <v>0.9382</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8742</v>
+        <v>0.8806</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3</v>
-      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1300,7 +1292,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -1314,7 +1306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1346,16 +1338,16 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>8.9</v>
+        <v>5.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9899</v>
+        <v>0.8953</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9912</v>
+        <v>0.9382</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1363,10 +1355,10 @@
         </is>
       </c>
       <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
         <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1429,16 +1421,16 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>6.73</v>
+        <v>6.76</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7768</v>
+        <v>0.546</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8361</v>
+        <v>0.6936</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7703</v>
+        <v>0.5255</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1446,10 +1438,10 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1490,13 +1482,9 @@
         <v>128</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0.35</v>
       </c>
@@ -1516,16 +1504,16 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>15.25</v>
+        <v>8.81</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9899</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9962</v>
+        <v>0.9937</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9872</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1536,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1560,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -1599,16 +1587,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>6.73</v>
+        <v>8.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8209</v>
+        <v>0.9899</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8752</v>
+        <v>0.9912</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8205</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1616,10 +1604,10 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1643,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -1682,16 +1670,16 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>6.74</v>
+        <v>8.83</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7881</v>
+        <v>0.884</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8625</v>
+        <v>0.9319</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7844</v>
+        <v>0.8742</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1768,13 +1756,13 @@
         <v>8.84</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9887</v>
+        <v>0.9836</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9912</v>
+        <v>0.9937</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9872</v>
+        <v>0.9831</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1785,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1816,7 +1804,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1848,16 +1836,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>8.85</v>
+        <v>8.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.9899</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8436</v>
+        <v>0.9912</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6751</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -1868,7 +1856,7 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1885,14 +1873,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -1931,16 +1919,16 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5.12</v>
+        <v>6.73</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8058</v>
+        <v>0.7768</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.8361</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7927</v>
+        <v>0.7703</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -1951,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1982,7 +1970,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1992,9 +1980,13 @@
         <v>128</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M19" t="n">
         <v>0.35</v>
       </c>
@@ -2014,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>8.859999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.71</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8537</v>
+        <v>0.9962</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6888</v>
+        <v>0.9872</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2031,7 +2023,7 @@
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>1</v>
@@ -2058,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -2097,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>8.84</v>
+        <v>6.73</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9836</v>
+        <v>0.8209</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9937</v>
+        <v>0.8752</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9831</v>
+        <v>0.8205</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2117,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2132,9 +2124,13 @@
       <c r="C21" t="n">
         <v>174</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -2176,24 +2172,28 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6936</v>
+        <v>0.71</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8386</v>
+        <v>0.8537</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6715</v>
+        <v>0.6888</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2207,12 +2207,16 @@
       <c r="C22" t="n">
         <v>174</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -2251,24 +2255,28 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2</v>
+        <v>8.85</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5334</v>
+        <v>0.8789</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6923</v>
+        <v>0.9332</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5135</v>
+        <v>0.8692</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2330,16 +2338,16 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9887</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9912</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9202</v>
+        <v>0.9872</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2347,10 +2355,10 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2391,13 +2399,9 @@
         <v>128</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>0.35</v>
       </c>
@@ -2417,16 +2421,16 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>14.75</v>
+        <v>8.85</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8903</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9382</v>
+        <v>0.8436</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8803</v>
+        <v>0.6751</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2434,10 +2438,10 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
@@ -2478,9 +2482,13 @@
         <v>128</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M25" t="n">
         <v>0.35</v>
       </c>
@@ -2500,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>9.01</v>
+        <v>15.18</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7415</v>
+        <v>0.8953</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8714</v>
+        <v>0.9395</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7196</v>
+        <v>0.8892</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2517,10 +2525,10 @@
         </is>
       </c>
       <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
         <v>2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2537,14 +2545,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -2583,16 +2591,16 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>6.72</v>
+        <v>5.11</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7856</v>
+        <v>0.9912</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8398</v>
+        <v>0.9912</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7879</v>
+        <v>0.9908</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2600,7 +2608,7 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
         <v>1</v>
@@ -2644,13 +2652,9 @@
         <v>128</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>0.35</v>
       </c>
@@ -2670,16 +2674,16 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>15.18</v>
+        <v>8.82</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8953</v>
+        <v>0.8789</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9395</v>
+        <v>0.9357</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8892</v>
+        <v>0.8701</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -2690,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2705,16 +2709,12 @@
       <c r="C28" t="n">
         <v>174</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -2753,28 +2753,24 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>8.82</v>
+        <v>0.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8789</v>
+        <v>0.5334</v>
       </c>
       <c r="U28" t="n">
-        <v>0.9357</v>
+        <v>0.6923</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8701</v>
+        <v>0.5135</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>3</v>
-      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2797,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -2836,16 +2832,16 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>6.66</v>
+        <v>8.85</v>
       </c>
       <c r="T29" t="n">
-        <v>0.7856</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>0.8373</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="V29" t="n">
-        <v>0.7863</v>
+        <v>0.9202</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -2853,10 +2849,10 @@
         </is>
       </c>
       <c r="X29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y29" t="n">
         <v>3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="30">
@@ -2887,7 +2883,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2897,9 +2893,13 @@
         <v>128</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M30" t="n">
         <v>0.35</v>
       </c>
@@ -2919,16 +2919,16 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>8.81</v>
+        <v>14.75</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9899</v>
+        <v>0.8903</v>
       </c>
       <c r="U30" t="n">
-        <v>0.9937</v>
+        <v>0.9382</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.8803</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2963,14 +2963,14 @@
         <v>1</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>6.69</v>
+        <v>9.01</v>
       </c>
       <c r="T31" t="n">
-        <v>0.8209</v>
+        <v>0.7415</v>
       </c>
       <c r="U31" t="n">
-        <v>0.8752</v>
+        <v>0.8714</v>
       </c>
       <c r="V31" t="n">
-        <v>0.8193</v>
+        <v>0.7196</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3085,16 +3085,16 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="T32" t="n">
-        <v>0.7919</v>
+        <v>0.7856</v>
       </c>
       <c r="U32" t="n">
-        <v>0.8474</v>
+        <v>0.8398</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7934</v>
+        <v>0.7879</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y32" t="n">
         <v>1</v>
@@ -3129,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -3168,16 +3168,16 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>8.85</v>
+        <v>6.66</v>
       </c>
       <c r="T33" t="n">
-        <v>0.9899</v>
+        <v>0.7856</v>
       </c>
       <c r="U33" t="n">
-        <v>0.9912</v>
+        <v>0.8373</v>
       </c>
       <c r="V33" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.7863</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3251,16 +3251,16 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>6.68</v>
+        <v>6.74</v>
       </c>
       <c r="T34" t="n">
-        <v>0.7995</v>
+        <v>0.7881</v>
       </c>
       <c r="U34" t="n">
-        <v>0.8752</v>
+        <v>0.8625</v>
       </c>
       <c r="V34" t="n">
-        <v>0.7965</v>
+        <v>0.7844</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3288,21 +3288,21 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3334,16 +3334,16 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>6.74</v>
+        <v>5.11</v>
       </c>
       <c r="T35" t="n">
-        <v>0.604</v>
+        <v>0.9899</v>
       </c>
       <c r="U35" t="n">
-        <v>0.7377</v>
+        <v>0.9937</v>
       </c>
       <c r="V35" t="n">
-        <v>0.5891</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -3381,13 +3381,9 @@
         <v>1</v>
       </c>
       <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>256</v>
       </c>
@@ -3417,28 +3413,24 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>6.72</v>
+        <v>4.12</v>
       </c>
       <c r="T36" t="n">
-        <v>0.7982</v>
+        <v>0.8026</v>
       </c>
       <c r="U36" t="n">
-        <v>0.8714</v>
+        <v>0.8844</v>
       </c>
       <c r="V36" t="n">
-        <v>0.8004</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1</v>
-      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3454,7 +3446,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -3464,9 +3456,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>256</v>
       </c>
@@ -3496,24 +3492,28 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>4.12</v>
+        <v>6.69</v>
       </c>
       <c r="T37" t="n">
-        <v>0.8026</v>
+        <v>0.8209</v>
       </c>
       <c r="U37" t="n">
-        <v>0.8844</v>
+        <v>0.8752</v>
       </c>
       <c r="V37" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8193</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3529,21 +3529,21 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3553,13 +3553,9 @@
         <v>128</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>0.35</v>
       </c>
@@ -3579,16 +3575,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>7.05</v>
+        <v>6.69</v>
       </c>
       <c r="T38" t="n">
-        <v>0.8436</v>
+        <v>0.7919</v>
       </c>
       <c r="U38" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.8474</v>
       </c>
       <c r="V38" t="n">
-        <v>0.834</v>
+        <v>0.7934</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -3596,7 +3592,7 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
         <v>1</v>
@@ -3616,19 +3612,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>256</v>
       </c>
@@ -3636,13 +3636,9 @@
         <v>128</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>0.35</v>
       </c>
@@ -3662,24 +3658,28 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>5.39</v>
+        <v>8.85</v>
       </c>
       <c r="T39" t="n">
-        <v>0.8026</v>
+        <v>0.9899</v>
       </c>
       <c r="U39" t="n">
-        <v>0.8857</v>
+        <v>0.9912</v>
       </c>
       <c r="V39" t="n">
-        <v>0.793</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
+      <c r="X39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3705,9 +3705,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>256</v>
       </c>
@@ -3737,24 +3741,28 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>21.06</v>
+        <v>6.68</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7924</v>
+        <v>0.7995</v>
       </c>
       <c r="U40" t="n">
-        <v>0.8658</v>
+        <v>0.8752</v>
       </c>
       <c r="V40" t="n">
-        <v>0.7904</v>
+        <v>0.7965</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
+      <c r="X40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3777,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -3794,13 +3802,9 @@
         <v>128</v>
       </c>
       <c r="K41" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>0.35</v>
       </c>
@@ -3820,16 +3824,16 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>15.28</v>
+        <v>6.74</v>
       </c>
       <c r="T41" t="n">
-        <v>0.8966</v>
+        <v>0.604</v>
       </c>
       <c r="U41" t="n">
-        <v>0.9395</v>
+        <v>0.7377</v>
       </c>
       <c r="V41" t="n">
-        <v>0.8894</v>
+        <v>0.5891</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -3837,10 +3841,10 @@
         </is>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3864,14 +3868,14 @@
         <v>1</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3881,13 +3885,9 @@
         <v>128</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>0.35</v>
       </c>
@@ -3907,16 +3907,16 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>14.38</v>
+        <v>6.72</v>
       </c>
       <c r="T42" t="n">
-        <v>0.8487</v>
+        <v>0.7982</v>
       </c>
       <c r="U42" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.8714</v>
       </c>
       <c r="V42" t="n">
-        <v>0.8374</v>
+        <v>0.8004</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
         <v>1</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -3954,9 +3954,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>256</v>
       </c>
@@ -3986,24 +3990,28 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>22.19</v>
+        <v>5.07</v>
       </c>
       <c r="T43" t="n">
-        <v>0.8827</v>
+        <v>0.9899</v>
       </c>
       <c r="U43" t="n">
-        <v>0.9281</v>
+        <v>0.9912</v>
       </c>
       <c r="V43" t="n">
-        <v>0.8718</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
+      <c r="X43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4019,14 +4027,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
@@ -4069,16 +4077,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>12.97</v>
+        <v>7.36</v>
       </c>
       <c r="T44" t="n">
-        <v>0.739</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="U44" t="n">
-        <v>0.7995</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="V44" t="n">
-        <v>0.7321</v>
+        <v>0.8808</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4086,10 +4094,10 @@
         </is>
       </c>
       <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
         <v>3</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -4106,14 +4114,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
@@ -4156,16 +4164,16 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>14.64</v>
+        <v>7.1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.826</v>
+        <v>0.9849</v>
       </c>
       <c r="U45" t="n">
-        <v>0.8764</v>
+        <v>0.9937</v>
       </c>
       <c r="V45" t="n">
-        <v>0.8267</v>
+        <v>0.9821</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4173,7 +4181,7 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y45" t="n">
         <v>1</v>
@@ -4191,21 +4199,21 @@
       <c r="C46" t="n">
         <v>174</v>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>256</v>
       </c>
@@ -4235,16 +4243,16 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.09</v>
+        <v>21.06</v>
       </c>
       <c r="T46" t="n">
-        <v>0.7869</v>
+        <v>0.7924</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8373</v>
+        <v>0.8658</v>
       </c>
       <c r="V46" t="n">
-        <v>0.7869</v>
+        <v>0.7904</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -4266,13 +4274,9 @@
       <c r="C47" t="n">
         <v>174</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -4292,13 +4296,9 @@
         <v>128</v>
       </c>
       <c r="K47" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>0.35</v>
       </c>
@@ -4318,28 +4318,24 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>13.92</v>
+        <v>0.2</v>
       </c>
       <c r="T47" t="n">
-        <v>0.7856</v>
+        <v>0.5334</v>
       </c>
       <c r="U47" t="n">
-        <v>0.8487</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="V47" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1</v>
-      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4362,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -4405,16 +4401,16 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>15.46</v>
+        <v>14.64</v>
       </c>
       <c r="T48" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="U48" t="n">
-        <v>0.9811</v>
+        <v>0.8764</v>
       </c>
       <c r="V48" t="n">
-        <v>0.9623</v>
+        <v>0.8267</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -4425,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4440,23 +4436,19 @@
       <c r="C49" t="n">
         <v>174</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -4466,13 +4458,9 @@
         <v>128</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>0.35</v>
       </c>
@@ -4492,28 +4480,24 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>14.3</v>
+        <v>0.09</v>
       </c>
       <c r="T49" t="n">
-        <v>0.8436</v>
+        <v>0.7869</v>
       </c>
       <c r="U49" t="n">
-        <v>0.9256</v>
+        <v>0.8373</v>
       </c>
       <c r="V49" t="n">
-        <v>0.8318</v>
+        <v>0.7869</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4579,16 +4563,16 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>15.25</v>
+        <v>13.92</v>
       </c>
       <c r="T50" t="n">
-        <v>0.8222</v>
+        <v>0.7856</v>
       </c>
       <c r="U50" t="n">
-        <v>0.8764</v>
+        <v>0.8487</v>
       </c>
       <c r="V50" t="n">
-        <v>0.8208</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -4599,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4614,19 +4598,23 @@
       <c r="C51" t="n">
         <v>174</v>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -4636,9 +4624,13 @@
         <v>128</v>
       </c>
       <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M51" t="n">
         <v>0.35</v>
       </c>
@@ -4658,24 +4650,28 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2</v>
+        <v>15.46</v>
       </c>
       <c r="T51" t="n">
-        <v>0.5334</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="U51" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.9811</v>
       </c>
       <c r="V51" t="n">
-        <v>0.5119</v>
+        <v>0.9623</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4741,16 +4737,16 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>15.4</v>
+        <v>15.05</v>
       </c>
       <c r="T52" t="n">
-        <v>0.9798</v>
+        <v>0.9899</v>
       </c>
       <c r="U52" t="n">
-        <v>0.9912</v>
+        <v>0.9962</v>
       </c>
       <c r="V52" t="n">
-        <v>0.9792</v>
+        <v>0.9896</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -4758,10 +4754,10 @@
         </is>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4785,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
@@ -4828,16 +4824,16 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>13.31</v>
+        <v>14.3</v>
       </c>
       <c r="T53" t="n">
-        <v>0.7617</v>
+        <v>0.8436</v>
       </c>
       <c r="U53" t="n">
-        <v>0.8222</v>
+        <v>0.9256</v>
       </c>
       <c r="V53" t="n">
-        <v>0.7537</v>
+        <v>0.8318</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -4845,10 +4841,10 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y53" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54">
@@ -4872,14 +4868,14 @@
         <v>1</v>
       </c>
       <c r="F54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -4915,16 +4911,16 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>13.09</v>
+        <v>15.4</v>
       </c>
       <c r="T54" t="n">
-        <v>0.7516</v>
+        <v>0.9798</v>
       </c>
       <c r="U54" t="n">
-        <v>0.8096</v>
+        <v>0.9912</v>
       </c>
       <c r="V54" t="n">
-        <v>0.7431</v>
+        <v>0.9792</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -4932,10 +4928,10 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4950,21 +4946,21 @@
       <c r="C55" t="n">
         <v>174</v>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>256</v>
       </c>
@@ -4972,9 +4968,13 @@
         <v>128</v>
       </c>
       <c r="K55" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M55" t="n">
         <v>0.35</v>
       </c>
@@ -4994,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.09</v>
+        <v>15.36</v>
       </c>
       <c r="T55" t="n">
-        <v>0.9899</v>
+        <v>0.8177</v>
       </c>
       <c r="U55" t="n">
-        <v>0.9912</v>
+        <v>0.8861</v>
       </c>
       <c r="V55" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.8156</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5077,16 +5077,16 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>15.23</v>
+        <v>15.28</v>
       </c>
       <c r="T56" t="n">
-        <v>0.8979</v>
+        <v>0.8966</v>
       </c>
       <c r="U56" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9395</v>
       </c>
       <c r="V56" t="n">
-        <v>0.8902</v>
+        <v>0.8894</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
         <v>3</v>
@@ -5114,19 +5114,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>256</v>
       </c>
@@ -5160,24 +5164,28 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>7.39</v>
+        <v>13.09</v>
       </c>
       <c r="T57" t="n">
-        <v>0.8827</v>
+        <v>0.7516</v>
       </c>
       <c r="U57" t="n">
-        <v>0.9395</v>
+        <v>0.8096</v>
       </c>
       <c r="V57" t="n">
-        <v>0.8699</v>
+        <v>0.7431</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
+      <c r="X57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5191,13 +5199,9 @@
       <c r="C58" t="n">
         <v>174</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -5217,13 +5221,9 @@
         <v>128</v>
       </c>
       <c r="K58" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>0.35</v>
       </c>
@@ -5243,28 +5243,24 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>15.05</v>
+        <v>0.09</v>
       </c>
       <c r="T58" t="n">
         <v>0.9899</v>
       </c>
       <c r="U58" t="n">
-        <v>0.9962</v>
+        <v>0.9912</v>
       </c>
       <c r="V58" t="n">
-        <v>0.9896</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1</v>
-      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5278,19 +5274,23 @@
       <c r="C59" t="n">
         <v>174</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -5300,9 +5300,13 @@
         <v>128</v>
       </c>
       <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M59" t="n">
         <v>0.35</v>
       </c>
@@ -5322,24 +5326,28 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.09</v>
+        <v>15.23</v>
       </c>
       <c r="T59" t="n">
-        <v>0.7844</v>
+        <v>0.8979</v>
       </c>
       <c r="U59" t="n">
-        <v>0.8361</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="V59" t="n">
-        <v>0.7867</v>
+        <v>0.8902</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
+      <c r="X59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5355,23 +5363,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>resnet50</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>256</v>
       </c>
@@ -5405,28 +5409,24 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>15.29</v>
+        <v>7.39</v>
       </c>
       <c r="T60" t="n">
-        <v>0.8197</v>
+        <v>0.8827</v>
       </c>
       <c r="U60" t="n">
-        <v>0.8865</v>
+        <v>0.9395</v>
       </c>
       <c r="V60" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8699</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X60" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>3</v>
-      </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5449,14 +5449,14 @@
         <v>1</v>
       </c>
       <c r="F61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -5492,16 +5492,16 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>15.47</v>
+        <v>15.25</v>
       </c>
       <c r="T61" t="n">
-        <v>0.9294</v>
+        <v>0.8222</v>
       </c>
       <c r="U61" t="n">
-        <v>0.971</v>
+        <v>0.8764</v>
       </c>
       <c r="V61" t="n">
-        <v>0.9247</v>
+        <v>0.8208</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="X61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="n">
         <v>3</v>
@@ -5529,14 +5529,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -5579,16 +5579,16 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>14.93</v>
+        <v>7.05</v>
       </c>
       <c r="T62" t="n">
-        <v>0.8121</v>
+        <v>0.8436</v>
       </c>
       <c r="U62" t="n">
-        <v>0.8689</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="V62" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.834</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5666,16 +5666,16 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>14.4</v>
+        <v>15.29</v>
       </c>
       <c r="T63" t="n">
-        <v>0.8247</v>
+        <v>0.8197</v>
       </c>
       <c r="U63" t="n">
-        <v>0.8625</v>
+        <v>0.8865</v>
       </c>
       <c r="V63" t="n">
-        <v>0.8242</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="X63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y63" t="n">
         <v>3</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="64">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5753,16 +5753,16 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>15.01</v>
+        <v>7.27</v>
       </c>
       <c r="T64" t="n">
-        <v>0.9899</v>
+        <v>0.8777</v>
       </c>
       <c r="U64" t="n">
-        <v>0.9962</v>
+        <v>0.9445</v>
       </c>
       <c r="V64" t="n">
-        <v>0.9896</v>
+        <v>0.8702</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="X64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -5840,16 +5840,16 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>15.1</v>
+        <v>13.31</v>
       </c>
       <c r="T65" t="n">
-        <v>0.8197</v>
+        <v>0.7617</v>
       </c>
       <c r="U65" t="n">
-        <v>0.884</v>
+        <v>0.8222</v>
       </c>
       <c r="V65" t="n">
-        <v>0.8192</v>
+        <v>0.7537</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="X65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -5877,21 +5877,21 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E66" t="b">
         <v>1</v>
       </c>
       <c r="F66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5927,16 +5927,16 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>14.38</v>
+        <v>6.92</v>
       </c>
       <c r="T66" t="n">
-        <v>0.826</v>
+        <v>0.8083</v>
       </c>
       <c r="U66" t="n">
-        <v>0.8663</v>
+        <v>0.8991</v>
       </c>
       <c r="V66" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.7929</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
@@ -5984,13 +5984,9 @@
         <v>128</v>
       </c>
       <c r="K67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
         <v>0.35</v>
       </c>
@@ -6010,16 +6006,16 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>15.36</v>
+        <v>22.19</v>
       </c>
       <c r="T67" t="n">
-        <v>0.8177</v>
+        <v>0.8827</v>
       </c>
       <c r="U67" t="n">
-        <v>0.8861</v>
+        <v>0.9281</v>
       </c>
       <c r="V67" t="n">
-        <v>0.8156</v>
+        <v>0.8718</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -6180,16 +6176,16 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>14.44</v>
+        <v>14.38</v>
       </c>
       <c r="T69" t="n">
-        <v>0.8663</v>
+        <v>0.8487</v>
       </c>
       <c r="U69" t="n">
-        <v>0.9319</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="V69" t="n">
-        <v>0.8555</v>
+        <v>0.8374</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6197,7 +6193,7 @@
         </is>
       </c>
       <c r="X69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y69" t="n">
         <v>1</v>
@@ -6215,9 +6211,13 @@
       <c r="C70" t="n">
         <v>174</v>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -6237,9 +6237,13 @@
         <v>128</v>
       </c>
       <c r="K70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M70" t="n">
         <v>0.35</v>
       </c>
@@ -6259,24 +6263,28 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.09</v>
+        <v>15.47</v>
       </c>
       <c r="T70" t="n">
-        <v>0.9899</v>
+        <v>0.9294</v>
       </c>
       <c r="U70" t="n">
-        <v>0.9912</v>
+        <v>0.971</v>
       </c>
       <c r="V70" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9247</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
+      <c r="X70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6306,7 +6314,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -6342,16 +6350,16 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>15.32</v>
+        <v>14.93</v>
       </c>
       <c r="T71" t="n">
-        <v>0.8298</v>
+        <v>0.8121</v>
       </c>
       <c r="U71" t="n">
-        <v>0.8852</v>
+        <v>0.8689</v>
       </c>
       <c r="V71" t="n">
-        <v>0.8286</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -6362,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -6386,14 +6394,14 @@
         <v>1</v>
       </c>
       <c r="F72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6403,9 +6411,13 @@
         <v>128</v>
       </c>
       <c r="K72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M72" t="n">
         <v>0.35</v>
       </c>
@@ -6425,16 +6437,16 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>8.81</v>
+        <v>14.4</v>
       </c>
       <c r="T72" t="n">
-        <v>0.8108</v>
+        <v>0.8247</v>
       </c>
       <c r="U72" t="n">
-        <v>0.918</v>
+        <v>0.8625</v>
       </c>
       <c r="V72" t="n">
-        <v>0.7945</v>
+        <v>0.8242</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -6442,10 +6454,10 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y72" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="73">
@@ -6472,9 +6484,13 @@
         <v>0</v>
       </c>
       <c r="G73" t="b">
-        <v>0</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>256</v>
       </c>
@@ -6508,24 +6524,28 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>15.3</v>
+        <v>15.01</v>
       </c>
       <c r="T73" t="n">
-        <v>0.8979</v>
+        <v>0.9899</v>
       </c>
       <c r="U73" t="n">
-        <v>0.9407</v>
+        <v>0.9962</v>
       </c>
       <c r="V73" t="n">
-        <v>0.8909</v>
+        <v>0.9896</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
+      <c r="X73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6548,7 +6568,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
@@ -6591,16 +6611,16 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>14.96</v>
+        <v>15.1</v>
       </c>
       <c r="T74" t="n">
-        <v>0.9899</v>
+        <v>0.8197</v>
       </c>
       <c r="U74" t="n">
-        <v>0.9962</v>
+        <v>0.884</v>
       </c>
       <c r="V74" t="n">
-        <v>0.9896</v>
+        <v>0.8192</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -6608,10 +6628,10 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -6678,16 +6698,16 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>15.47</v>
+        <v>14.38</v>
       </c>
       <c r="T75" t="n">
-        <v>0.8209</v>
+        <v>0.826</v>
       </c>
       <c r="U75" t="n">
-        <v>0.889</v>
+        <v>0.8663</v>
       </c>
       <c r="V75" t="n">
-        <v>0.8178</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
@@ -6695,10 +6715,10 @@
         </is>
       </c>
       <c r="X75" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="Y75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6713,79 +6733,1079 @@
       <c r="C76" t="n">
         <v>174</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>256</v>
+      </c>
+      <c r="J76" t="n">
+        <v>128</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N76" t="n">
+        <v>50</v>
+      </c>
+      <c r="O76" t="n">
+        <v>10</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R76" t="b">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.7844</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.8361</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.7867</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C77" t="n">
+        <v>174</v>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>keynet_hardnet</t>
         </is>
       </c>
-      <c r="E76" t="b">
-        <v>1</v>
-      </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="b">
+        <v>0</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>megadescriptor-l-384</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>256</v>
-      </c>
-      <c r="J76" t="n">
-        <v>128</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" t="inlineStr">
+      <c r="I77" t="n">
+        <v>256</v>
+      </c>
+      <c r="J77" t="n">
+        <v>128</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N77" t="n">
+        <v>50</v>
+      </c>
+      <c r="O77" t="n">
+        <v>10</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R77" t="b">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C78" t="n">
+        <v>174</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>256</v>
+      </c>
+      <c r="J78" t="n">
+        <v>128</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N78" t="n">
+        <v>50</v>
+      </c>
+      <c r="O78" t="n">
+        <v>10</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R78" t="b">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0.9681999999999999</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C79" t="n">
+        <v>174</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>256</v>
+      </c>
+      <c r="J79" t="n">
+        <v>128</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N79" t="n">
+        <v>50</v>
+      </c>
+      <c r="O79" t="n">
+        <v>10</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R79" t="b">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.7995</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C80" t="n">
+        <v>174</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>256</v>
+      </c>
+      <c r="J80" t="n">
+        <v>128</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N80" t="n">
+        <v>50</v>
+      </c>
+      <c r="O80" t="n">
+        <v>10</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R80" t="b">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.8852</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.8286</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C81" t="n">
+        <v>174</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="b">
+        <v>0</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>256</v>
+      </c>
+      <c r="J81" t="n">
+        <v>128</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N81" t="n">
+        <v>50</v>
+      </c>
+      <c r="O81" t="n">
+        <v>10</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.8108</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C82" t="n">
+        <v>174</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="b">
+        <v>0</v>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>256</v>
+      </c>
+      <c r="J82" t="n">
+        <v>128</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N82" t="n">
+        <v>50</v>
+      </c>
+      <c r="O82" t="n">
+        <v>10</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R82" t="b">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.8979</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.9407</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C83" t="n">
+        <v>174</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="b">
+        <v>0</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>256</v>
+      </c>
+      <c r="J83" t="n">
+        <v>128</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N83" t="n">
+        <v>50</v>
+      </c>
+      <c r="O83" t="n">
+        <v>10</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X83" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C84" t="n">
+        <v>174</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>256</v>
+      </c>
+      <c r="J84" t="n">
+        <v>128</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N84" t="n">
+        <v>50</v>
+      </c>
+      <c r="O84" t="n">
+        <v>10</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.8209</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0.8178</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C85" t="n">
+        <v>174</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>256</v>
+      </c>
+      <c r="J85" t="n">
+        <v>128</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N85" t="n">
+        <v>50</v>
+      </c>
+      <c r="O85" t="n">
+        <v>10</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0.9319</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X85" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C86" t="n">
+        <v>174</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>256</v>
+      </c>
+      <c r="J86" t="n">
+        <v>128</v>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N86" t="n">
+        <v>50</v>
+      </c>
+      <c r="O86" t="n">
+        <v>10</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R86" t="b">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.8026</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C87" t="n">
+        <v>174</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" t="b">
+        <v>0</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>256</v>
+      </c>
+      <c r="J87" t="n">
+        <v>128</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N87" t="n">
+        <v>50</v>
+      </c>
+      <c r="O87" t="n">
+        <v>10</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C88" t="n">
+        <v>174</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>256</v>
+      </c>
+      <c r="J88" t="n">
+        <v>128</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M76" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N76" t="n">
-        <v>50</v>
-      </c>
-      <c r="O76" t="n">
-        <v>10</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R76" t="b">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0.9908</v>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>WildlifeReID10k</t>
-        </is>
-      </c>
-      <c r="X76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>1</v>
+      <c r="M88" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N88" t="n">
+        <v>50</v>
+      </c>
+      <c r="O88" t="n">
+        <v>10</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0.9892</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
